--- a/PrimarySources/readable/CHTR-Critical-Tables.xlsx
+++ b/PrimarySources/readable/CHTR-Critical-Tables.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="4" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="1" state="visible" r:id="rId1"/>
@@ -35,23 +34,23 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Q2_2026'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Deals_Competition'!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0;(#,##0)"/>
-    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00;(#,##0.00);"/>
+    <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\);"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="26">
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -59,57 +58,154 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="000F2944"/>
+      <color rgb="FF0F2944"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="005A6570"/>
+      <color rgb="FF5A6570"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF5A6570"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FF0F2944"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <i val="1"/>
+      <color rgb="FF5A6570"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
       <i val="1"/>
-      <color rgb="005A6570"/>
+      <color rgb="FF5A6570"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
+      <family val="1"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FF1B3A4B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <i val="1"/>
+      <color rgb="FF475467"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="FF0F2944"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <i val="1"/>
+      <color rgb="FF5A6570"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <i val="1"/>
+      <color rgb="FF5A6570"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
       <b val="1"/>
-      <color rgb="001B3A4B"/>
+      <color rgb="FF1B3A4B"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
       <i val="1"/>
-      <color rgb="00475467"/>
+      <color rgb="FF475467"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -122,36 +218,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F2944"/>
+        <fgColor rgb="FF0F2944"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F6"/>
+        <fgColor rgb="FFEEF2F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E7"/>
+        <fgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF4"/>
+        <fgColor rgb="FFE8EEF4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A4B"/>
+        <fgColor rgb="FF1B3A4B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -161,73 +257,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D3C7"/>
+        <color rgb="FFD9D3C7"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D3C7"/>
+        <color rgb="FFD9D3C7"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D3C7"/>
+        <color rgb="FFD9D3C7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D3C7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D0D5DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D5DD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D5DD"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D5DD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D5DD"/>
+        <color rgb="FFD9D3C7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
       <right style="thin">
-        <color rgb="00D0D5DD"/>
+        <color rgb="FFD0D5DD"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D5DD"/>
+        <color rgb="FFD0D5DD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D5DD"/>
+        <color rgb="FFD0D5DD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -235,153 +289,307 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -741,112 +949,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" style="7" min="1" max="1"/>
+    <col width="110" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.7265625" customWidth="1" style="7" min="3" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Charter Communications (CHTR) — critical tables</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>Disclosed figures only. Assignment anchor: end of Q1 2026 (31 Mar 2026). Q2 2026 (30 Jun 2026) is later public fact from the 24 Jul 2026 10-Q / Ex99.1. Verify disputed numbers in the original 10-K / 10-Q / Exhibit 99.1 HTML.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Rule / fact</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="42" customHeight="1" s="2">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>Customers in thousands. Dollars in millions except EPS, ARPU, share counts, and leverage ratios.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="42" customHeight="1" s="2">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>Customer-count basis</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>Do not mix bases. Q4 2025 restated customer relationships to include all mobile (including mobile-only) and added total connectivity customers. 2024–2026 figures here use the restated basis from the FY2025 10-K / Q1 and Q2 2026 Ex99.1. FY2023 customer counts are pre-restatement.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="42" customHeight="1" s="2">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>Non-GAAP</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Adjusted EBITDA and free cash flow are Charter-defined non-GAAP measures. Reconciliations are on the EBITDA_FCF sheet.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="42" customHeight="1" s="2">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>What is excluded</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Full 10-K note tables, iXBRL tags, trending-schedule chrome, rural difference rows, and assignment commentary. IR PDF earnings releases duplicate Exhibit 99.1.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="42" customHeight="1" s="2">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>10-K FY2025 (filed 30 Jan 2026); 10-Q Q1 2026 (filed 24 Apr 2026); 10-Q Q2 2026 (filed 24 Jul 2026); Exhibit 99.1 FY2025, Q1 2026, and Q2 2026; Cox PR 16 May 2025. Quarterly trend lines also use the unofficial IR trending extract (cross-check Ex99.1).</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="42" customHeight="1" s="2">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>Workbook map</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>Snapshot → Customers → Quarterly_Trend → Revenue → Income_Statement → EBITDA_FCF → Capex → Balance_Sheet → Q1_2026 → Q2_2026 → Deals_Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" s="2">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>Font</t>
+        </is>
+      </c>
+      <c r="B11" s="114" t="inlineStr">
+        <is>
+          <t>Georgia on every sheet. Agent updates to this workbook use Georgia (bold/size/color unchanged).</t>
         </is>
       </c>
     </row>
@@ -856,356 +1077,356 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14" customWidth="1" style="7" min="2" max="3"/>
+    <col width="12" customWidth="1" style="7" min="4" max="4"/>
+    <col width="48" customWidth="1" style="7" min="5" max="5"/>
+    <col width="8.7265625" customWidth="1" style="7" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Q1 2026 vs Q1 2025 — the quarter the case is anchored to</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>Exhibit 99.1 dated 24 Apr 2026 and Form 10-Q quarter ended 31 Mar 2026. Dollars in millions; customers in thousands.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Q1 2025</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>Total revenue ($M)</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="99" t="n">
         <v>13735</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="99" t="n">
         <v>13597</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="98" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="105" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Internet revenue ($M)</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="100" t="n">
         <v>5930</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="100" t="n">
         <v>5852</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="96" t="n">
         <v>-0.013</v>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="76" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Mobile service revenue ($M)</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="101" t="n">
         <v>914</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="101" t="n">
         <v>1052</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="95" t="n">
         <v>0.151</v>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="71" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Video revenue ($M)</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="100" t="n">
         <v>3580</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="100" t="n">
         <v>3252</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="96" t="n">
         <v>-0.092</v>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="76" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Advertising sales ($M)</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="101" t="n">
         <v>340</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="101" t="n">
         <v>358</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="95" t="n">
         <v>0.053</v>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="71" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>Adjusted EBITDA ($M)</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="99" t="n">
         <v>5763</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="99" t="n">
         <v>5637</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="98" t="n">
         <v>-0.022</v>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="105" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Net income to Charter shareholders ($M)</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="101" t="n">
         <v>1217</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="101" t="n">
         <v>1163</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="95" t="n">
         <v>-0.044</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="71" t="inlineStr">
         <is>
           <t>10-Q / course table</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Capital expenditures ($M)</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="100" t="n">
         <v>2399</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="100" t="n">
         <v>2855</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="96" t="n">
         <v>0.19</v>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="76" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>Free cash flow ($M)</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="99" t="n">
         <v>1564</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="99" t="n">
         <v>1372</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="98" t="n">
         <v>-0.123</v>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="105" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Internet customers, end of period (000s)</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="100" t="n">
         <v>30024</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="100" t="n">
         <v>29560</v>
       </c>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="D14" s="76" t="n"/>
+      <c r="E14" s="76" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Internet quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="101" t="n">
         <v>-59</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="101" t="n">
         <v>-120</v>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="D15" s="71" t="n"/>
+      <c r="E15" s="71" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Mobile lines, end of period (000s)</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="100" t="n">
         <v>10365</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="100" t="n">
         <v>12134</v>
       </c>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="D16" s="76" t="n"/>
+      <c r="E16" s="76" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>Mobile quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="101" t="n">
         <v>507</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="101" t="n">
         <v>368</v>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="D17" s="71" t="n"/>
+      <c r="E17" s="71" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Shares repurchased (millions of shares)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="73" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="100" t="n">
         <v>4.3</v>
       </c>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="D18" s="76" t="n"/>
+      <c r="E18" s="76" t="inlineStr">
         <is>
           <t>Ex99.1: 4.3 million shares for $963 million</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="20" ht="48" customHeight="1" s="2">
+      <c r="A20" s="83" t="inlineStr">
         <is>
           <t>10-Q: revenues −$138M vs Q1 2025 'primarily due to higher seamless entertainment allocation, partly offset by growth in connectivity revenue.' Adj. EBITDA also hit by $75M of one-time favorable adjustments in Q1 2025. Remaining buyback authorization ~$179M excluding Liberty Broadband purchases; A/N standing repurchase agreement suspended Aug 2025 pending Cox close.</t>
         </is>
@@ -1218,411 +1439,411 @@
     <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B3A4B"/>
+    <tabColor rgb="FF1B3A4B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14" customWidth="1" style="7" min="2" max="3"/>
+    <col width="12" customWidth="1" style="7" min="4" max="4"/>
+    <col width="48" customWidth="1" style="7" min="5" max="5"/>
+    <col width="8.7265625" customWidth="1" style="7" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>Q2 2026 vs Q2 2025 — later public facts after the assignment anchor</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>Exhibit 99.1 dated 24 Jul 2026 and Form 10-Q quarter ended 30 Jun 2026. Dollars in millions; customers in thousands. Assignment still anchors recommendations to Q1 2026.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="2">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="104" t="inlineStr">
         <is>
           <t>Total revenue ($M)</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="108" t="n">
         <v>13766</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="108" t="n">
         <v>13526</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="109" t="n">
         <v>-0.017</v>
       </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>Internet revenue ($M)</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="108" t="n">
         <v>5969</v>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="108" t="n">
         <v>5776</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="109" t="n">
         <v>-0.032</v>
       </c>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="104" t="inlineStr">
         <is>
           <t>Mobile service revenue ($M)</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="108" t="n">
         <v>921</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="108" t="n">
         <v>1095</v>
       </c>
-      <c r="D7" s="50" t="n">
+      <c r="D7" s="109" t="n">
         <v>0.189</v>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="104" t="inlineStr">
         <is>
           <t>Video revenue ($M)</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="108" t="n">
         <v>3488</v>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="108" t="n">
         <v>3149</v>
       </c>
-      <c r="D8" s="50" t="n">
+      <c r="D8" s="109" t="n">
         <v>-0.097</v>
       </c>
-      <c r="E8" s="46" t="inlineStr">
+      <c r="E8" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="104" t="inlineStr">
         <is>
           <t>Advertising sales ($M)</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="108" t="n">
         <v>371</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="108" t="n">
         <v>416</v>
       </c>
-      <c r="D9" s="50" t="n">
+      <c r="D9" s="109" t="n">
         <v>0.123</v>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="104" t="inlineStr">
         <is>
           <t>Adjusted EBITDA ($M)</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="108" t="n">
         <v>5693</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="108" t="n">
         <v>5449</v>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="109" t="n">
         <v>-0.043</v>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>Net income to Charter shareholders ($M)</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="108" t="n">
         <v>1301</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="108" t="n">
         <v>1292</v>
       </c>
-      <c r="D11" s="50" t="n">
+      <c r="D11" s="109" t="n">
         <v>-0.007</v>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="104" t="inlineStr">
         <is>
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="B12" s="51" t="n">
+      <c r="B12" s="110" t="n">
         <v>9.18</v>
       </c>
-      <c r="C12" s="51" t="n">
+      <c r="C12" s="110" t="n">
         <v>10.66</v>
       </c>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="inlineStr">
+      <c r="D12" s="104" t="n"/>
+      <c r="E12" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="104" t="inlineStr">
         <is>
           <t>Capital expenditures ($M)</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="108" t="n">
         <v>2874</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="108" t="n">
         <v>2871</v>
       </c>
-      <c r="D13" s="50" t="n">
+      <c r="D13" s="109" t="n">
         <v>-0.001</v>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E13" s="104" t="inlineStr">
         <is>
           <t>Ex99.1 / 10-Q</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>Free cash flow ($M)</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="108" t="n">
         <v>1046</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="108" t="n">
         <v>969</v>
       </c>
-      <c r="D14" s="50" t="n">
+      <c r="D14" s="109" t="n">
         <v>-0.074</v>
       </c>
-      <c r="E14" s="46" t="inlineStr">
+      <c r="E14" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>Operating cash flow ($M)</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="108" t="n">
         <v>3600</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="108" t="n">
         <v>3925</v>
       </c>
-      <c r="D15" s="50" t="n">
+      <c r="D15" s="109" t="n">
         <v>0.09</v>
       </c>
-      <c r="E15" s="46" t="inlineStr">
+      <c r="E15" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="104" t="inlineStr">
         <is>
           <t>Internet customers, end of period (000s)</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="108" t="n">
         <v>29908</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="108" t="n">
         <v>29388</v>
       </c>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="46" t="inlineStr">
+      <c r="D16" s="104" t="n"/>
+      <c r="E16" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="104" t="inlineStr">
         <is>
           <t>Internet quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="108" t="n">
         <v>-116</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="108" t="n">
         <v>-172</v>
       </c>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="46" t="inlineStr">
+      <c r="D17" s="104" t="n"/>
+      <c r="E17" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="104" t="inlineStr">
         <is>
           <t>Mobile lines, end of period (000s)</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="108" t="n">
         <v>10856</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="108" t="n">
         <v>12540</v>
       </c>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="inlineStr">
+      <c r="D18" s="104" t="n"/>
+      <c r="E18" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>Mobile quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="108" t="n">
         <v>491</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="108" t="n">
         <v>406</v>
       </c>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="46" t="inlineStr">
+      <c r="D19" s="104" t="n"/>
+      <c r="E19" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="104" t="inlineStr">
         <is>
           <t>Video quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="108" t="n">
         <v>-80</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="108" t="n">
         <v>-21</v>
       </c>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="46" t="inlineStr">
+      <c r="D20" s="104" t="n"/>
+      <c r="E20" s="104" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="A21" s="104" t="inlineStr">
         <is>
           <t>Shares repurchased (millions of shares)</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="52" t="n">
+      <c r="B21" s="104" t="n"/>
+      <c r="C21" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="46" t="inlineStr">
+      <c r="D21" s="104" t="n"/>
+      <c r="E21" s="104" t="inlineStr">
         <is>
           <t>Ex99.1: 4.0 million shares for $838 million</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="72" customHeight="1">
-      <c r="A23" s="53" t="inlineStr">
+    <row r="23" ht="72" customHeight="1" s="2">
+      <c r="A23" s="112" t="inlineStr">
         <is>
           <t>10-Q MD&amp;A: “The competitive environment continued to challenge our Internet customer growth in the second quarter of 2026 and we lost 172,000 Internet customers.” Transition expenses $65 million in Q2 ($89 million H1). Programmer-app costs netted in video revenue $251 million vs $67 million in Q2 2025. Open-market note repurchases: $1.2 billion principal for $1.0 billion cash. Leverage 4.18x. Cox still pending at quarter-end: contribution cash $650 million; combined entity to assume ~$12.4 billion Cox net debt (updated from $500 million / $12.6 billion in the FY2025 10-K).</t>
         </is>
@@ -1636,568 +1857,568 @@
     <mergeCell ref="A23:E23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" style="2" min="1" max="1"/>
+    <col width="36" customWidth="1" style="2" min="2" max="2"/>
+    <col width="88" customWidth="1" style="2" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Pending transactions, competition, capital allocation</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>As stated in 10-K FY2025, 10-Q Q1 2026, 10-Q Q2 2026, and the 16 May 2025 Cox press release. Course-brief stock-price language is labeled Brief.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>As stated</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Cox (10-K)</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>Agreement date</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>16 May 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Cox (10-K)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>Cash — equity sale</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>$3.5 billion to Cox Enterprises</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Cox (10-K)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>Cash — contribution</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>$500 million (10-K; Cox PR lists $4 billion cash total)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Cox (10-K)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>Convertible preferred</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="76" t="inlineStr">
         <is>
           <t>$6.0 billion liquidation preference; 6.875% dividend; conversion price $477.41</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Cox (10-K)</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>Common units issued</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>~33.6 million Charter Holdings common units</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Cox (10-K)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>Cox net debt assumed</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="76" t="inlineStr">
         <is>
           <t>~$12.6 billion outstanding net debt and finance leases</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>Cox (10-Q Q2)</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>Cash — contribution (updated)</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="104" t="inlineStr">
         <is>
           <t>$650 million (was $500 million in FY2025 10-K / Q1 10-Q)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="104" t="inlineStr">
         <is>
           <t>Cox (10-Q Q2)</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>Cox net debt assumed (updated)</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="104" t="inlineStr">
         <is>
           <t>~$12.4 billion outstanding net debt and finance leases (was $12.6 billion in FY2025 10-K)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="104" t="inlineStr">
         <is>
           <t>Cox (10-Q Q2)</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="104" t="inlineStr">
         <is>
           <t>Status at 30 Jun 2026</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="104" t="inlineStr">
         <is>
           <t>Still pending. Q2 10-Q: required to fund ~$4.2 billion cash purchase price at closing.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>Cox (PR)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Stated enterprise value</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="71" t="inlineStr">
         <is>
           <t>~$34.5 billion ($21.9B equity + $12.6B net debt and other obligations)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>Cox (PR)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>Ownership at close</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="76" t="inlineStr">
         <is>
           <t>~23% fully diluted as-converted / as-exchanged, pro forma Liberty, vs 31 Mar 2025 share count</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>Cox (Brief)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Expected close</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="71" t="inlineStr">
         <is>
           <t>Mid-2026 (Team Case Brief)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Liberty Broadband</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>Agreement date</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="76" t="inlineStr">
         <is>
           <t>12 Nov 2024</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>Liberty Broadband</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="71" t="inlineStr">
         <is>
           <t>Exchange ratio</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="71" t="inlineStr">
         <is>
           <t>0.236 Charter Class A share per Liberty Broadband share</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>Liberty Broadband</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="76" t="inlineStr">
         <is>
           <t>Liberty’s Charter stake</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="76" t="inlineStr">
         <is>
           <t>~41.5 million CHTR Class A shares at 31 Dec 2025</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>Liberty Broadband</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>GCI Alaska spin-off</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="71" t="inlineStr">
         <is>
           <t>Completed 14 Jul 2025</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Competition (10-K)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="76" t="inlineStr">
         <is>
           <t>AT&amp;T 100 Mbps+ overlap</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>~27% of footprint</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>Competition (10-K)</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="71" t="inlineStr">
         <is>
           <t>Verizon 100 Mbps+ overlap</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="71" t="inlineStr">
         <is>
           <t>~16% of footprint</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>Competition (10-K)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>Other Internet rivals named</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="76" t="inlineStr">
         <is>
           <t>FTTH, FWA (national MNOs), satellite, DSL</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="71" t="inlineStr">
         <is>
           <t>FY2025 purchases (Ex99.1)</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="71" t="inlineStr">
         <is>
           <t>17.1 million shares/units for ~$5.4 billion</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="72" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="76" t="inlineStr">
         <is>
           <t>Q1 2026 purchases</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="76" t="inlineStr">
         <is>
           <t>4.3 million Class A shares for $963 million</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="46" t="inlineStr">
+      <c r="A26" s="104" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="B26" s="46" t="inlineStr">
+      <c r="B26" s="104" t="inlineStr">
         <is>
           <t>Q2 2026 purchases</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="104" t="inlineStr">
         <is>
           <t>4.0 million Class A shares for $838 million; also $1.2B principal of CCO/CCOH notes for $1.0B cash</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="46" t="inlineStr">
+      <c r="A27" s="104" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="104" t="inlineStr">
         <is>
           <t>Since Sep 2016 through 30 Jun 2026</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C27" s="104" t="inlineStr">
         <is>
           <t>~188.0 million shares/units for ~$80.6 billion (incl. Liberty Broadband and A/N)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="46" t="inlineStr">
+      <c r="A28" s="104" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="104" t="inlineStr">
         <is>
           <t>Remaining board authority 30 Jun 2026</t>
         </is>
       </c>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="C28" s="104" t="inlineStr">
         <is>
           <t>$365 million excluding purchases from Liberty Broadband (10-Q Q2)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="46" t="inlineStr">
+    <row r="29" ht="48" customHeight="1" s="2">
+      <c r="A29" s="104" t="inlineStr">
         <is>
           <t>Leverage (10-Q Q2)</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="104" t="inlineStr">
         <is>
           <t>Net debt / LTM Adj. EBITDA</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C29" s="104" t="inlineStr">
         <is>
           <t>4.18x at 30 Jun 2026; long-term target after Closing stated as 3.5x</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t>Buybacks</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="71" t="inlineStr">
         <is>
           <t>Since Sep 2016 through YE2025</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="71" t="inlineStr">
         <is>
           <t>~179.7 million shares/units for ~$78.8 billion (incl. Liberty Broadband and A/N)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="72" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="76" t="inlineStr">
         <is>
           <t>Employees YE2025</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="76" t="inlineStr">
         <is>
           <t>~91,900 FTEs, described as 100% U.S.-based</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="71" t="inlineStr">
         <is>
           <t>Non-affiliate market value</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="71" t="inlineStr">
         <is>
           <t>~$37.1 billion at 30 Jun 2025 (10-K cover calculation)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="72" t="inlineStr">
         <is>
           <t>Brief only</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="76" t="inlineStr">
         <is>
           <t>Five-year stock performance</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="76" t="inlineStr">
         <is>
           <t>Brief: stock lost roughly 80% over the past five years</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="68" t="inlineStr">
         <is>
           <t>Brief only</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="71" t="inlineStr">
         <is>
           <t>Q1 2026 earnings-day move</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="71" t="inlineStr">
         <is>
           <t>Brief: stock fell about 25% in a single day after the Q1 2026 release</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="A36" s="113" t="inlineStr">
         <is>
           <t>Cox cash is $3.5B + $500M in the FY2025 10-K and $4B in the May 2025 PR (same total, different split). Q2 2026 10-Q updates contribution cash to $650 million and assumed Cox net debt to ~$12.4 billion. Brief rows are assignment language, not SEC filings. Q2 10-Q still describes the Cox and Liberty transactions as pending.</t>
         </is>
@@ -2210,424 +2431,421 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14" customWidth="1" style="7" min="2" max="6"/>
+    <col width="42" customWidth="1" style="7" min="7" max="7"/>
+    <col width="8.7265625" customWidth="1" style="7" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Snapshot — Charter consolidated</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>FY from 10-K FY2025. Q1/Q2 2026 from Exhibit 99.1 / 10-Q. Customers 2024–2026 restated; FY2023 customers are the prior methodology.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Total revenue ($M)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="69" t="n">
         <v>54607</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="69" t="n">
         <v>55085</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="69" t="n">
         <v>54774</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="69" t="n">
         <v>13597</v>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="70" t="n">
         <v>13526</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="71" t="inlineStr">
         <is>
           <t>10-K FY2025; Ex99.1 Q1/Q2 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Adjusted EBITDA ($M)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="73" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="74" t="n">
         <v>22569</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="74" t="n">
         <v>22708</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="74" t="n">
         <v>5637</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="75" t="n">
         <v>5449</v>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="76" t="inlineStr">
         <is>
           <t>10-K / Ex99.1 (non-GAAP)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Net income to Charter shareholders ($M)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="69" t="n">
         <v>4557</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="69" t="n">
         <v>5083</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="69" t="n">
         <v>4987</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="69" t="n">
         <v>1163</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="70" t="n">
         <v>1292</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="71" t="inlineStr">
         <is>
           <t>10-K; Ex99.1 Q1 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="77" t="n">
         <v>29.99</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="77" t="n">
         <v>34.97</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="77" t="n">
         <v>36.21</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="73" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="78" t="n">
         <v>10.66</v>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="76" t="inlineStr">
         <is>
           <t>10-K FY2025; Ex99.1 Q2 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Free cash flow ($M)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="69" t="n">
         <v>4257</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="69" t="n">
         <v>5004</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="69" t="n">
         <v>1372</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="70" t="n">
         <v>969</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="71" t="inlineStr">
         <is>
           <t>Ex99.1 (non-GAAP)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Capital expenditures ($M)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="74" t="n">
         <v>11269</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="74" t="n">
         <v>11659</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="74" t="n">
         <v>2855</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="75" t="n">
         <v>2871</v>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="76" t="inlineStr">
         <is>
           <t>10-K Item 7; Ex99.1 Q1 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Total customer relationships (000s)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="69" t="n">
         <v>32126</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="69" t="n">
         <v>32214</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="69" t="n">
         <v>31846</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="69" t="n">
         <v>31683</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="70" t="n">
         <v>31499</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="71" t="inlineStr">
         <is>
           <t>10-K; Ex99.1. FY2023 old basis</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Total Internet customers (000s)</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="74" t="n">
         <v>30588</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="74" t="n">
         <v>30083</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="74" t="n">
         <v>29680</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="74" t="n">
         <v>29560</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="75" t="n">
         <v>29388</v>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="76" t="inlineStr">
         <is>
           <t>10-K; Ex99.1. FY2023 old basis</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>Total mobile lines (000s)</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="69" t="n">
         <v>7766</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="69" t="n">
         <v>9858</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="69" t="n">
         <v>11766</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="69" t="n">
         <v>12134</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="70" t="n">
         <v>12540</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="71" t="inlineStr">
         <is>
           <t>10-K restated 2024–25; FY2023 old basis</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Estimated passings (000s)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="73" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="74" t="n">
         <v>56861</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="74" t="n">
         <v>58399</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="74" t="n">
         <v>58661</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="75" t="n">
         <v>58981</v>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="76" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Class A shares outstanding</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="79" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="79" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="69" t="n">
         <v>126631549</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="69" t="n">
         <v>122984536</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="80" t="n">
         <v>119277492</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="71" t="inlineStr">
         <is>
           <t>10-K cover; 10-Q Q1 and Q2 covers</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Net debt / LTM Adj. EBITDA (x)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="73" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="73" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="81" t="n">
         <v>4.15</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="81" t="n">
         <v>4.15</v>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F16" s="82" t="n">
         <v>4.18</v>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="76" t="inlineStr">
         <is>
           <t>10-K; 10-Q (company’s stated ratio)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18" ht="48" customHeight="1" s="2">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>n/a: FY2023 Adjusted EBITDA, FCF, and capex are not shown because the FY2024 10-K reports those CCO Holdings figures, which are not comparable to Charter consolidated. Q2 diluted EPS is as reported ($10.66). Passings are year-end / quarter-end, not a FY average. Q2 2026 is later than the assignment anchor.</t>
         </is>
@@ -2640,614 +2858,613 @@
     <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" style="7" min="1" max="1"/>
+    <col width="16" customWidth="1" style="7" min="2" max="3"/>
+    <col width="14" customWidth="1" style="7" min="4" max="4"/>
+    <col width="16" customWidth="1" style="7" min="5" max="6"/>
+    <col width="14" customWidth="1" style="7" min="7" max="7"/>
+    <col width="16" customWidth="1" style="7" min="8" max="8"/>
+    <col width="22" customWidth="1" style="7" min="9" max="9"/>
+    <col width="8.7265625" customWidth="1" style="7" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Customers — restated basis (thousands except ARPU)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>Year-end from 10-K FY2025 Item 1 (same as Ex99.1 FY2025). 31 Mar 2026 from Ex99.1 Q1 2026. 30 Jun 2026 from Ex99.1 Q2 2026.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="4" ht="29" customHeight="1" s="2">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>31 Dec 2024</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>31 Dec 2025</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>YE change</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>31 Mar 2026</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>Q1 seq. net adds</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>30 Jun 2026</t>
         </is>
       </c>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="H4" s="67" t="inlineStr">
         <is>
           <t>Q2 seq. net adds</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="67" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Estimated passings</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="69" t="n">
         <v>56861</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="69" t="n">
         <v>58399</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="69" t="n">
         <v>1538</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="69" t="n">
         <v>58661</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="69" t="n">
         <v>262</v>
       </c>
-      <c r="G5" s="32" t="n">
+      <c r="G5" s="70" t="n">
         <v>58981</v>
       </c>
-      <c r="H5" s="32" t="n">
+      <c r="H5" s="70" t="n">
         <v>320</v>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="84" t="inlineStr">
         <is>
           <t>Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Residential customer relationships</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="74" t="n">
         <v>29964</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="74" t="n">
         <v>29609</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="74" t="n">
         <v>-355</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="74" t="n">
         <v>29452</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="74" t="n">
         <v>-157</v>
       </c>
-      <c r="G6" s="33" t="n">
+      <c r="G6" s="75" t="n">
         <v>29276</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="75" t="n">
         <v>-176</v>
       </c>
-      <c r="I6" s="38" t="inlineStr">
+      <c r="I6" s="85" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Small business customer relationships</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="69" t="n">
         <v>2250</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="69" t="n">
         <v>2237</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="69" t="n">
         <v>-13</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="69" t="n">
         <v>2231</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="69" t="n">
         <v>-6</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="70" t="n">
         <v>2223</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H7" s="70" t="n">
         <v>-8</v>
       </c>
-      <c r="I7" s="37" t="inlineStr">
+      <c r="I7" s="84" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>Total customer relationships</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="87" t="n">
         <v>32214</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="87" t="n">
         <v>31846</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="87" t="n">
         <v>-368</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="87" t="n">
         <v>31683</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="87" t="n">
         <v>-163</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="88" t="n">
         <v>31499</v>
       </c>
-      <c r="H8" s="39" t="n">
+      <c r="H8" s="88" t="n">
         <v>-184</v>
       </c>
-      <c r="I8" s="40" t="inlineStr">
+      <c r="I8" s="89" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Total connectivity customers</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="69" t="n">
         <v>30845</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="69" t="n">
         <v>30640</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="69" t="n">
         <v>-205</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="69" t="n">
         <v>30520</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="69" t="n">
         <v>-120</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="70" t="n">
         <v>30375</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H9" s="70" t="n">
         <v>-145</v>
       </c>
-      <c r="I9" s="37" t="inlineStr">
+      <c r="I9" s="84" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Residential Internet</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="74" t="n">
         <v>28034</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="74" t="n">
         <v>27641</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="74" t="n">
         <v>-393</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="74" t="n">
         <v>27524</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="74" t="n">
         <v>-117</v>
       </c>
-      <c r="G10" s="33" t="n">
+      <c r="G10" s="75" t="n">
         <v>27358</v>
       </c>
-      <c r="H10" s="33" t="n">
+      <c r="H10" s="75" t="n">
         <v>-166</v>
       </c>
-      <c r="I10" s="38" t="inlineStr">
+      <c r="I10" s="85" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Small-business Internet</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="69" t="n">
         <v>2049</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="69" t="n">
         <v>2039</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="69" t="n">
         <v>-10</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="69" t="n">
         <v>2036</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="70" t="n">
         <v>2030</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="H11" s="70" t="n">
         <v>-6</v>
       </c>
-      <c r="I11" s="37" t="inlineStr">
+      <c r="I11" s="84" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>Total Internet customers</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="87" t="n">
         <v>30083</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="87" t="n">
         <v>29680</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="87" t="n">
         <v>-403</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="87" t="n">
         <v>29560</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="87" t="n">
         <v>-120</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="88" t="n">
         <v>29388</v>
       </c>
-      <c r="H12" s="39" t="n">
+      <c r="H12" s="88" t="n">
         <v>-172</v>
       </c>
-      <c r="I12" s="40" t="inlineStr">
+      <c r="I12" s="89" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>Residential mobile lines</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="69" t="n">
         <v>9543</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="69" t="n">
         <v>11370</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="69" t="n">
         <v>1827</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="69" t="n">
         <v>11714</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="69" t="n">
         <v>344</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="70" t="n">
         <v>12099</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="70" t="n">
         <v>385</v>
       </c>
-      <c r="I13" s="37" t="inlineStr">
+      <c r="I13" s="84" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Small-business mobile lines</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="74" t="n">
         <v>315</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="74" t="n">
         <v>396</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="74" t="n">
         <v>81</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="74" t="n">
         <v>420</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="74" t="n">
         <v>24</v>
       </c>
-      <c r="G14" s="33" t="n">
+      <c r="G14" s="75" t="n">
         <v>441</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="75" t="n">
         <v>21</v>
       </c>
-      <c r="I14" s="38" t="inlineStr">
+      <c r="I14" s="85" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="86" t="inlineStr">
         <is>
           <t>Total mobile lines</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="87" t="n">
         <v>9858</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="87" t="n">
         <v>11766</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="87" t="n">
         <v>1908</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="87" t="n">
         <v>12134</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="87" t="n">
         <v>368</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="88" t="n">
         <v>12540</v>
       </c>
-      <c r="H15" s="39" t="n">
+      <c r="H15" s="88" t="n">
         <v>406</v>
       </c>
-      <c r="I15" s="40" t="inlineStr">
+      <c r="I15" s="89" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Total video customers</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="74" t="n">
         <v>12892</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="74" t="n">
         <v>12605</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="74" t="n">
         <v>-287</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="74" t="n">
         <v>12545</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="74" t="n">
         <v>-60</v>
       </c>
-      <c r="G16" s="33" t="n">
+      <c r="G16" s="75" t="n">
         <v>12524</v>
       </c>
-      <c r="H16" s="33" t="n">
+      <c r="H16" s="75" t="n">
         <v>-21</v>
       </c>
-      <c r="I16" s="38" t="inlineStr">
+      <c r="I16" s="85" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>Total voice customers</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="69" t="n">
         <v>6884</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="69" t="n">
         <v>6046</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="69" t="n">
         <v>-838</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="69" t="n">
         <v>5872</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="69" t="n">
         <v>-174</v>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="70" t="n">
         <v>5694</v>
       </c>
-      <c r="H17" s="32" t="n">
+      <c r="H17" s="70" t="n">
         <v>-178</v>
       </c>
-      <c r="I17" s="37" t="inlineStr">
+      <c r="I17" s="84" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Mid-market &amp; large business PSUs</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="74" t="n">
         <v>340</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="74" t="n">
         <v>357</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="74" t="n">
         <v>360</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="74" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="33" t="n">
+      <c r="G18" s="75" t="n">
         <v>364</v>
       </c>
-      <c r="H18" s="33" t="n">
+      <c r="H18" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="38" t="inlineStr">
+      <c r="I18" s="85" t="inlineStr">
         <is>
           <t>10-K / Ex99.1</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="19" ht="26" customHeight="1" s="2">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>Monthly residential revenue / customer ($)</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="90" t="n">
         <v>118.71</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="90" t="n">
         <v>119.05</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="90" t="n">
         <v>0.34</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="90" t="n">
         <v>118.44</v>
       </c>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="41" t="n">
+      <c r="F19" s="71" t="n"/>
+      <c r="G19" s="91" t="n">
         <v>117.52</v>
       </c>
-      <c r="H19" s="42" t="n"/>
-      <c r="I19" s="37" t="inlineStr">
+      <c r="H19" s="92" t="n"/>
+      <c r="I19" s="84" t="inlineStr">
         <is>
           <t>10-K YE ARPU; Ex99.1 Q1/Q2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>Monthly small-business revenue / customer ($)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="77" t="n">
         <v>161.97</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="77" t="n">
         <v>161.5</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="77" t="n">
         <v>-0.47</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="77" t="n">
         <v>162.71</v>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="43" t="n">
+      <c r="F20" s="76" t="n"/>
+      <c r="G20" s="93" t="n">
         <v>165.27</v>
       </c>
-      <c r="H20" s="44" t="n"/>
-      <c r="I20" s="38" t="inlineStr">
+      <c r="H20" s="94" t="n"/>
+      <c r="I20" s="85" t="inlineStr">
         <is>
           <t>10-K; Ex99.1</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="22" ht="48" customHeight="1" s="2">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>Q4 2025 restatement: customer relationships include all mobile customers (including mobile-only); connectivity = Internet and/or mobile. Sequential net adds for passings are the increase in estimated passings in the quarter, not customer net adds. Voice Q2 net adds (−178) are from Ex99.1 release text. Accounts &gt;60 days past due: ~82,300 at 31 Dec 2025 vs ~102,500 at 31 Dec 2024 (10-K footnote).</t>
         </is>
@@ -3260,460 +3477,451 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11" customWidth="1" style="7" min="2" max="12"/>
+    <col width="12" customWidth="1" style="7" min="13" max="13"/>
+    <col width="18" customWidth="1" style="7" min="14" max="14"/>
+    <col width="8.7265625" customWidth="1" style="7" min="15" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Quarterly trend — five lines that drive the case</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>Customers (000s) and dollars ($M). 2023–2025 from unofficial IR trending schedule (verify vs Ex99.1). 2026 1Q/2Q from Ex99.1. Restated customer methodology. FY columns are year totals (revenue/EBITDA/FCF) or year-end (customers).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>2024 1Q</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>2024 2Q</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>2024 3Q</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>2024 4Q</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>2024 FY</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>2025 1Q</t>
         </is>
       </c>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="H4" s="67" t="inlineStr">
         <is>
           <t>2025 2Q</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="67" t="inlineStr">
         <is>
           <t>2025 3Q</t>
         </is>
       </c>
-      <c r="J4" s="31" t="inlineStr">
+      <c r="J4" s="67" t="inlineStr">
         <is>
           <t>2025 4Q</t>
         </is>
       </c>
-      <c r="K4" s="31" t="inlineStr">
+      <c r="K4" s="67" t="inlineStr">
         <is>
           <t>2025 FY</t>
         </is>
       </c>
-      <c r="L4" s="31" t="inlineStr">
+      <c r="L4" s="67" t="inlineStr">
         <is>
           <t>2026 1Q</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr">
+      <c r="M4" s="67" t="inlineStr">
         <is>
           <t>2026 2Q</t>
         </is>
       </c>
-      <c r="N4" s="31" t="inlineStr">
+      <c r="N4" s="67" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Total Internet customers (000s)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="69" t="n">
         <v>30518</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="69" t="n">
         <v>30370</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="69" t="n">
         <v>30260</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="69" t="n">
         <v>30083</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="69" t="n">
         <v>30083</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="69" t="n">
         <v>30024</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="69" t="n">
         <v>29908</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="69" t="n">
         <v>29799</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="69" t="n">
         <v>29680</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="69" t="n">
         <v>29680</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="69" t="n">
         <v>29560</v>
       </c>
-      <c r="M5" s="32" t="n">
+      <c r="M5" s="70" t="n">
         <v>29388</v>
       </c>
-      <c r="N5" s="37" t="inlineStr">
+      <c r="N5" s="84" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Internet quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="74" t="n">
         <v>-72</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="74" t="n">
         <v>-148</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="74" t="n">
         <v>-110</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="74" t="n">
         <v>-177</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="74" t="n">
         <v>-507</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="74" t="n">
         <v>-59</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="74" t="n">
         <v>-116</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="74" t="n">
         <v>-109</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="74" t="n">
         <v>-119</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="74" t="n">
         <v>-403</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L6" s="74" t="n">
         <v>-120</v>
       </c>
-      <c r="M6" s="33" t="n">
+      <c r="M6" s="75" t="n">
         <v>-172</v>
       </c>
-      <c r="N6" s="38" t="inlineStr">
+      <c r="N6" s="85" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Total mobile lines (000s)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="69" t="n">
         <v>8244</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="69" t="n">
         <v>8796</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="69" t="n">
         <v>9336</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="69" t="n">
         <v>9858</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="69" t="n">
         <v>9858</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="69" t="n">
         <v>10365</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="69" t="n">
         <v>10856</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="69" t="n">
         <v>11338</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="69" t="n">
         <v>11766</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="69" t="n">
         <v>11766</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="69" t="n">
         <v>12134</v>
       </c>
-      <c r="M7" s="32" t="n">
+      <c r="M7" s="70" t="n">
         <v>12540</v>
       </c>
-      <c r="N7" s="37" t="inlineStr">
+      <c r="N7" s="84" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Mobile quarterly net adds (000s)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="74" t="n">
         <v>483</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="74" t="n">
         <v>552</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="74" t="n">
         <v>540</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="74" t="n">
         <v>522</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="74" t="n">
         <v>2097</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="74" t="n">
         <v>507</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="74" t="n">
         <v>491</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="74" t="n">
         <v>482</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="74" t="n">
         <v>428</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="74" t="n">
         <v>1908</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="74" t="n">
         <v>368</v>
       </c>
-      <c r="M8" s="33" t="n">
+      <c r="M8" s="75" t="n">
         <v>406</v>
       </c>
-      <c r="N8" s="38" t="inlineStr">
+      <c r="N8" s="85" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Total revenue ($M)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="69" t="n">
         <v>13679</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="69" t="n">
         <v>13685</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="69" t="n">
         <v>13795</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="69" t="n">
         <v>13926</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="69" t="n">
         <v>55085</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="69" t="n">
         <v>13735</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="69" t="n">
         <v>13766</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="69" t="n">
         <v>13672</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="69" t="n">
         <v>13601</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="69" t="n">
         <v>54774</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="69" t="n">
         <v>13597</v>
       </c>
-      <c r="M9" s="32" t="n">
+      <c r="M9" s="70" t="n">
         <v>13526</v>
       </c>
-      <c r="N9" s="37" t="inlineStr">
+      <c r="N9" s="84" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Adjusted EBITDA ($M)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="74" t="n">
         <v>5497</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="74" t="n">
         <v>5665</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="74" t="n">
         <v>5647</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="74" t="n">
         <v>5760</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="74" t="n">
         <v>22569</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="74" t="n">
         <v>5763</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="74" t="n">
         <v>5693</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="74" t="n">
         <v>5561</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="74" t="n">
         <v>5691</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="74" t="n">
         <v>22708</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="74" t="n">
         <v>5637</v>
       </c>
-      <c r="M10" s="33" t="n">
+      <c r="M10" s="75" t="n">
         <v>5449</v>
       </c>
-      <c r="N10" s="38" t="inlineStr">
+      <c r="N10" s="85" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Free cash flow ($M)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="69" t="n">
         <v>358</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="69" t="n">
         <v>1296</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="69" t="n">
         <v>1619</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="69" t="n">
         <v>984</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="69" t="n">
         <v>4257</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="69" t="n">
         <v>1564</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="69" t="n">
         <v>1046</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="69" t="n">
         <v>1621</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="69" t="n">
         <v>773</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="69" t="n">
         <v>5004</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="69" t="n">
         <v>1372</v>
       </c>
-      <c r="M11" s="32" t="n">
+      <c r="M11" s="70" t="n">
         <v>969</v>
       </c>
-      <c r="N11" s="37" t="inlineStr">
+      <c r="N11" s="84" t="inlineStr">
         <is>
           <t>Trending / Ex99.1</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="13" ht="48" customHeight="1" s="2">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>FY customer figures are period-end, not averages. FY net adds are the sum of four quarters. Internet loss of 120,000 in Q1 2026 vs 59,000 in Q1 2025 is the operating print the Team Case Brief treats as the earnings-day trigger. Q2 2026 Internet net adds were −172,000 (Ex99.1 Q2 2026).</t>
         </is>
@@ -3726,384 +3934,382 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14" customWidth="1" style="7" min="2" max="5"/>
+    <col width="12" customWidth="1" style="7" min="6" max="6"/>
+    <col width="14" customWidth="1" style="7" min="7" max="7"/>
+    <col width="8.7265625" customWidth="1" style="7" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Revenue by service offering ($M)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>FY from 10-K FY2025 Item 7. FY2023 from 10-K FY2024 / FY2025 notes (revenue is not affected by the customer restatement). Q1/Q2 from Ex99.1.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="4" ht="29" customHeight="1" s="2">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>FY25 vs FY24</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="69" t="n">
         <v>23032</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="69" t="n">
         <v>23360</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="69" t="n">
         <v>23765</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="69" t="n">
         <v>5852</v>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="70" t="n">
         <v>5776</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="95" t="n">
         <v>0.017</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Mobile service</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="74" t="n">
         <v>2243</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="74" t="n">
         <v>3083</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="74" t="n">
         <v>3762</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="74" t="n">
         <v>1052</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="75" t="n">
         <v>1095</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="96" t="n">
         <v>0.22</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>Connectivity (Internet + mobile)</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="87" t="n">
         <v>26443</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="87" t="n">
         <v>27527</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="87" t="n">
         <v>6904</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="88" t="n">
         <v>6871</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="98" t="n">
         <v>0.041</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="74" t="n">
         <v>16351</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="74" t="n">
         <v>15129</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="74" t="n">
         <v>13703</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="74" t="n">
         <v>3252</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="75" t="n">
         <v>3149</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="96" t="n">
         <v>-0.094</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="69" t="n">
         <v>1510</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="69" t="n">
         <v>1437</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="69" t="n">
         <v>1350</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="69" t="n">
         <v>338</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="70" t="n">
         <v>331</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="95" t="n">
         <v>-0.06</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>Residential revenue</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="87" t="n">
         <v>43136</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="87" t="n">
         <v>43009</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="87" t="n">
         <v>42580</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="87" t="n">
         <v>10494</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="88" t="n">
         <v>10351</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="98" t="n">
         <v>-0.01</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Small business</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="69" t="n">
         <v>4353</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="69" t="n">
         <v>4376</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="69" t="n">
         <v>4346</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="69" t="n">
         <v>1090</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="70" t="n">
         <v>1104</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="95" t="n">
         <v>-0.007</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Mid-market &amp; large business</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="74" t="n">
         <v>2770</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="74" t="n">
         <v>2878</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="74" t="n">
         <v>2969</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="74" t="n">
         <v>749</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="75" t="n">
         <v>761</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="96" t="n">
         <v>0.032</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>Commercial revenue</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="87" t="n">
         <v>7123</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="87" t="n">
         <v>7254</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="87" t="n">
         <v>7315</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="87" t="n">
         <v>1839</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="88" t="n">
         <v>1865</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="98" t="n">
         <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Advertising sales</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="74" t="n">
         <v>1551</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="74" t="n">
         <v>1780</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="74" t="n">
         <v>1468</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="74" t="n">
         <v>358</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="75" t="n">
         <v>416</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="96" t="n">
         <v>-0.176</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="69" t="n">
         <v>2797</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="69" t="n">
         <v>3042</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="69" t="n">
         <v>3411</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="69" t="n">
         <v>906</v>
       </c>
-      <c r="F15" s="32" t="n">
+      <c r="F15" s="70" t="n">
         <v>894</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="95" t="n">
         <v>0.121</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="87" t="n">
         <v>54607</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="87" t="n">
         <v>55085</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="87" t="n">
         <v>54774</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="87" t="n">
         <v>13597</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="88" t="n">
         <v>13526</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="98" t="n">
         <v>-0.006</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18" ht="48" customHeight="1" s="2">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>About 89% of FY2025 and FY2024 revenue is monthly subscription fees (10-K MD&amp;A). Advertising −$312M YoY in 2025 'primarily due to a decrease in political revenue.' Internet +$405M YoY = +$785M rate/mix and −$380M from fewer average residential Internet customers.</t>
         </is>
@@ -4116,256 +4322,255 @@
     <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" style="7" min="1" max="1"/>
+    <col width="16" customWidth="1" style="7" min="2" max="4"/>
+    <col width="8.7265625" customWidth="1" style="7" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Consolidated income statement ($M except EPS and shares)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>10-K FY2025 statements of operations. Three years as reported for Charter Communications, Inc.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>Revenues</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="99" t="n">
         <v>54607</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="99" t="n">
         <v>55085</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="99" t="n">
         <v>54774</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Operating costs and expenses</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="100" t="n">
         <v>33405</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="100" t="n">
         <v>33167</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="100" t="n">
         <v>32739</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Depreciation and amortization</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="101" t="n">
         <v>8696</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="101" t="n">
         <v>8673</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="101" t="n">
         <v>8711</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Other operating expenses, net</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="100" t="n">
         <v>-53</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="100" t="n">
         <v>127</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="100" t="n">
         <v>416</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="86" t="inlineStr">
         <is>
           <t>Income from operations</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="99" t="n">
         <v>12559</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="99" t="n">
         <v>13118</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="99" t="n">
         <v>12908</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Interest expense, net</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="100" t="n">
         <v>-5188</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="100" t="n">
         <v>-5229</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="100" t="n">
         <v>-5042</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Other expenses, net</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="101" t="n">
         <v>-517</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="101" t="n">
         <v>-387</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="101" t="n">
         <v>-408</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Income tax expense</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="100" t="n">
         <v>-1593</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="100" t="n">
         <v>-1649</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="100" t="n">
         <v>-1692</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>Consolidated net income</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="101" t="n">
         <v>5261</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="101" t="n">
         <v>5853</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="101" t="n">
         <v>5766</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>Net income attributable to Charter shareholders</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="99" t="n">
         <v>4557</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="99" t="n">
         <v>5083</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="99" t="n">
         <v>4987</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="90" t="n">
         <v>29.99</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="90" t="n">
         <v>34.97</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="90" t="n">
         <v>36.21</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Diluted weighted-average shares</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="74" t="n">
         <v>151966313</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="74" t="n">
         <v>145363771</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="74" t="n">
         <v>137743676</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18" ht="48" customHeight="1" s="2">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Net income to shareholders fell in 2025 while diluted EPS rose because buybacks reduced diluted shares from 145.4 million to 137.7 million.</t>
         </is>
@@ -4378,298 +4583,297 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14" customWidth="1" style="7" min="2" max="4"/>
+    <col width="12" customWidth="1" style="7" min="5" max="5"/>
+    <col width="8.7265625" customWidth="1" style="7" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Adjusted EBITDA and free cash flow ($M)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>Charter’s stated non-GAAP reconciliations, 10-K FY2025 / Ex99.1. Q1 from Ex99.1 Q1 2026. Q2 from Ex99.1 Q2 2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Net income attributable to Charter shareholders</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="101" t="n">
         <v>5083</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="101" t="n">
         <v>4987</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="101" t="n">
         <v>1163</v>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="E5" s="70" t="n">
         <v>1292</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>+ Noncontrolling interest</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="100" t="n">
         <v>770</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="100" t="n">
         <v>779</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="100" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="75" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>+ Interest expense, net</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="101" t="n">
         <v>5229</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="101" t="n">
         <v>5042</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="101" t="n">
         <v>1256</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="70" t="n">
         <v>1276</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>+ Income tax expense</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="100" t="n">
         <v>1649</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="100" t="n">
         <v>1692</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="100" t="n">
         <v>465</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="75" t="n">
         <v>475</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>+ Depreciation and amortization</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="101" t="n">
         <v>8673</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="101" t="n">
         <v>8711</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="101" t="n">
         <v>2211</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="70" t="n">
         <v>2197</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>+ Stock compensation</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="100" t="n">
         <v>651</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="100" t="n">
         <v>673</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="100" t="n">
         <v>203</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="75" t="n">
         <v>138</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>+ Other, net</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="101" t="n">
         <v>514</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="101" t="n">
         <v>824</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="101" t="n">
         <v>139</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="70" t="n">
         <v>-161</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>Adjusted EBITDA</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="99" t="n">
         <v>22569</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="99" t="n">
         <v>22708</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="99" t="n">
         <v>5637</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="88" t="n">
         <v>5449</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="101" t="n">
         <v>14430</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="101" t="n">
         <v>16077</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="101" t="n">
         <v>4304</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="70" t="n">
         <v>3925</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>− Purchases of PP&amp;E</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="100" t="n">
         <v>-11269</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="100" t="n">
         <v>-11659</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="100" t="n">
         <v>-2855</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="75" t="n">
         <v>-2871</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>± Change in accrued capex</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="101" t="n">
         <v>1096</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="101" t="n">
         <v>586</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="101" t="n">
         <v>-77</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="70" t="n">
         <v>-85</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="99" t="n">
         <v>4257</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="99" t="n">
         <v>5004</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="99" t="n">
         <v>1372</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="88" t="n">
         <v>969</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18" ht="48" customHeight="1" s="2">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Q1 recon lines from unofficial trending (totals match Ex99.1). Q2 recon from Ex99.1 addendum: NI 1,292 + NCI 232 + interest 1,276 + tax 475 + D&amp;A 2,197 + stock 138 + other (161) = Adj. EBITDA 5,449. OCF 3,925 − PP&amp;E 2,871 + accrued capex (85) = FCF 969.</t>
         </is>
@@ -4682,300 +4886,299 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14" customWidth="1" style="7" min="2" max="4"/>
+    <col width="12" customWidth="1" style="7" min="5" max="5"/>
+    <col width="8.7265625" customWidth="1" style="7" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Capital expenditures — NCTA categories ($M)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>10-K FY2025 Item 7. Q1 2026 from Ex99.1 / 10-Q / unofficial trending. Q2 2026 NCTA categories from 10-Q Q2 2026. 2026 full-year expectation ~$11.4 billion excluding Cox.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Customer premise equipment</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="69" t="n">
         <v>2172</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="69" t="n">
         <v>2260</v>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="45" t="n">
+      <c r="E5" s="102" t="n">
         <v>654</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Scalable infrastructure</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="74" t="n">
         <v>1422</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="74" t="n">
         <v>1536</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="74" t="n">
         <v>310</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="75" t="n">
         <v>336</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Upgrade/rebuild</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="69" t="n">
         <v>1771</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="69" t="n">
         <v>1937</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="69" t="n">
         <v>675</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="70" t="n">
         <v>657</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Support capital</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="74" t="n">
         <v>1688</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="74" t="n">
         <v>1986</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="74" t="n">
         <v>390</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="75" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="86" t="inlineStr">
         <is>
           <t>Capex excluding line extensions</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="87" t="n">
         <v>7053</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="87" t="n">
         <v>7719</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="87" t="n">
         <v>2043</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="88" t="n">
         <v>2141</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Subsidized rural construction line extensions</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="74" t="n">
         <v>2144</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="74" t="n">
         <v>2202</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="74" t="n">
         <v>426</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="75" t="n">
         <v>390</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Other line extensions</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="69" t="n">
         <v>2072</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="69" t="n">
         <v>1738</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="69" t="n">
         <v>386</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="70" t="n">
         <v>340</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>Total line extensions</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="87" t="n">
         <v>4216</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="87" t="n">
         <v>3940</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="87" t="n">
         <v>812</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="88" t="n">
         <v>730</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>Total capital expenditures</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="87" t="n">
         <v>11269</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="87" t="n">
         <v>11659</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="87" t="n">
         <v>2855</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="88" t="n">
         <v>2871</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Of which: commercial services</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="74" t="n">
         <v>1437</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="74" t="n">
         <v>1201</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="74" t="n">
         <v>286</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="75" t="n">
         <v>293</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Of which: rural construction initiative</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="69" t="n">
         <v>2152</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="69" t="n">
         <v>2208</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="69" t="n">
         <v>427</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="70" t="n">
         <v>391</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Of which: mobile</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="74" t="n">
         <v>245</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="74" t="n">
         <v>267</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="74" t="n">
         <v>60</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="75" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18" ht="48" customHeight="1" s="2">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Q1 2026 category rows (except CPE, which the trending extract dropped) are from the unofficial 1Q26 trending schedule; totals match Ex99.1 ($2,855 total; $812 line extensions). Q2 2026 categories are from the 10-Q NCTA table. Transition capex (Cox integration prep) was $34 million in Q2 2026 (10-Q footnote g). Rural since 2022: $7.7B spent, ~1.3 million passings activated (10-K Item 1). Network evolution expected largely complete by end of 2027.</t>
         </is>
@@ -4988,368 +5191,368 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2944"/>
+    <tabColor rgb="FF0F2944"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" style="7" min="1" max="1"/>
+    <col width="78" customWidth="1" style="7" min="2" max="2"/>
+    <col width="16" customWidth="1" style="7" min="3" max="4"/>
+    <col width="8.7265625" customWidth="1" style="7" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1" s="2">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Balance sheet highlights and leverage ($M)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="2">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>10-K FY2025 consolidated balance sheets. 30 Jun 2026 from Ex99.1 Q2 2026 condensed balance sheet. Leverage and liquidity from 10-Q Q1 and Q2 2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>31 Dec 2024</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>31 Dec 2025</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>30 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="69" t="n">
         <v>459</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="69" t="n">
         <v>477</v>
       </c>
-      <c r="D5" s="32" t="n">
+      <c r="D5" s="70" t="n">
         <v>509</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="74" t="n">
         <v>4233</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="74" t="n">
         <v>5144</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="75" t="n">
         <v>4973</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Property, plant and equipment, net</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="69" t="n">
         <v>42913</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="69" t="n">
         <v>46444</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="70" t="n">
         <v>47955</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Franchises (indefinite-lived)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="74" t="n">
         <v>67462</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="74" t="n">
         <v>67471</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="75" t="n">
         <v>67471</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="69" t="n">
         <v>29674</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="69" t="n">
         <v>29710</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="70" t="n">
         <v>29710</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="87" t="n">
         <v>150020</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="87" t="n">
         <v>154213</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="88" t="n">
         <v>155618</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Current portion of long-term debt</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="69" t="n">
         <v>1799</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="69" t="n">
         <v>750</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="70" t="n">
         <v>999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="87" t="n">
         <v>92134</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="87" t="n">
         <v>94006</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="88" t="n">
         <v>92960</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>Equipment installment plan financing</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="69" t="n">
         <v>1072</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="69" t="n">
         <v>1447</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="70" t="n">
         <v>1596</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Deferred income taxes</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="74" t="n">
         <v>18845</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="74" t="n">
         <v>19841</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="75" t="n">
         <v>20237</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Total Charter shareholders’ equity</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="69" t="n">
         <v>15587</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="69" t="n">
         <v>16054</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="70" t="n">
         <v>16952</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Noncontrolling interests</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="74" t="n">
         <v>4120</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="74" t="n">
         <v>4465</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="75" t="n">
         <v>4949</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="86" t="inlineStr">
         <is>
           <t>Total shareholders’ equity</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="87" t="n">
         <v>19707</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="87" t="n">
         <v>20519</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="88" t="n">
         <v>21901</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="103" t="inlineStr">
         <is>
           <t>Leverage and liquidity (as stated)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>As stated</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Net debt / LTM Adjusted EBITDA</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>4.15x at 31 Dec 2025 and 31 Mar 2026; 4.18x at 30 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>Stated range into Cox close</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="68" t="inlineStr">
         <is>
           <t>Near midpoint of 4.0–4.5x, pro forma for Liberty Broadband</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>Stated long-term target after Cox close</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>3.5x (Q2 10-Q; Q1 10-Q had said 3.5–3.75x)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>Cash on hand</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="68" t="inlineStr">
         <is>
           <t>~$517 million at 31 Mar 2026; $509 million at 30 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="72" t="inlineStr">
         <is>
           <t>Available under credit facilities</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>~$4.6 billion at 31 Mar 2026; ~$3.7 billion at 30 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>Franchise carrying value</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="68" t="inlineStr">
         <is>
           <t>~$67.5B (44% of assets at YE2025); &gt;10% cushion vs fair value at 31 Oct 2025 test</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="46" t="inlineStr">
+      <c r="A29" s="104" t="inlineStr">
         <is>
           <t>Principal amount of debt 30 Jun 2026</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="104" t="inlineStr">
         <is>
           <t>$93.8 billion (10-Q Q2: $12.5B credit facility, $54.7B IG notes, $26.7B HY notes)</t>
         </is>
@@ -5361,6 +5564,6 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>